--- a/docs/melta-harakteristiki.xlsx
+++ b/docs/melta-harakteristiki.xlsx
@@ -1424,7 +1424,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>biolut-condi-fresh-1l</t>
+          <t>biolut-liquid-soap-aloe-5l</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1434,17 +1434,17 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Biolut Condi Fresh, кондиционер для белья (этикетка PL/RU), Vegan</t>
+          <t>Biolut Antibacterial, жидкое мыло Aloe Vera</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Vegan</t>
+          <t>Деликатное очищение; 100% смывается с кожи; Эффективная защита от бактерий</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>1 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
@@ -1464,7 +1464,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>biolut-oxygen-1kg</t>
+          <t>biolut-liquid-soap-aloe-05l</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1474,17 +1474,17 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Biolut Oxygen, пятновыводитель-очиститель с активным кислородом</t>
+          <t>Biolut Antibacterial, жидкое мыло Aloe Vera</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Пятновыводитель; Очиститель для всего; С активным кислородом</t>
+          <t>Деликатное очищение; 100% смывается с кожи; Эффективная защита от бактерий</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>1 кг</t>
+          <t>0,5 л</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
@@ -1504,7 +1504,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>biolut-professional-gel-color-5l</t>
+          <t>biolut-condi-fresh-1l</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1514,17 +1514,17 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Biolut Professional Color, гель для стирки цветного белья (165 стирок)</t>
+          <t>Biolut Condi Fresh, кондиционер для белья (этикетка PL/RU), Vegan</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>165 стирок</t>
+          <t>Vegan</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>1 л</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
@@ -1544,7 +1544,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>biolut-professional-gel-5l</t>
+          <t>biolut-oxygen-1kg</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1554,17 +1554,17 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Biolut Professional, гель для стирки (165 стирок)</t>
+          <t>Biolut Oxygen, пятновыводитель-очиститель с активным кислородом</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>165 стирок</t>
+          <t>Пятновыводитель; Очиститель для всего; С активным кислородом</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>1 кг</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
@@ -1584,7 +1584,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>biolut-gel-wash-color-5l</t>
+          <t>biolut-professional-gel-color-5l</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Biolut gel wash Color, гель для стирки цветного белья, 160 стирок</t>
+          <t>Biolut Professional Color, гель для стирки цветного белья (165 стирок)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Для цветного белья; 160 стирок</t>
+          <t>165 стирок</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1624,7 +1624,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>biolut-antizhir-500ml</t>
+          <t>biolut-professional-gel-5l</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1634,17 +1634,17 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Biolut Антижир, профессиональная бытовая химия</t>
+          <t>Biolut Professional, гель для стирки (165 стирок)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Для плит, духовок, грилей и мультиварок; Эффективен от жира, нагара и копоти; Эфирные масла: для плит, духовок, грилей и мультиварок</t>
+          <t>165 стирок</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>500 мл</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr"/>
@@ -1664,7 +1664,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>biolut-dish-gel-aloe-sensitive-5l</t>
+          <t>biolut-gel-wash-color-5l</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1674,10 +1674,14 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Biolut, гель для посуды «Алоэ вера» Sensitive</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr"/>
+          <t>Biolut gel wash Color, гель для стирки цветного белья, 160 стирок</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Для цветного белья; 160 стирок</t>
+        </is>
+      </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
           <t>5 л</t>
@@ -1700,7 +1704,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>biolut-dish-gel-aloe-sensitive-1l</t>
+          <t>biolut-antizhir-500ml</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1710,17 +1714,17 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Biolut, гель для посуды «Алоэ вера» Sensitive</t>
+          <t>Biolut Антижир, профессиональная бытовая химия</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Густая формула; Биоразлагаемый состав; Антибактериальный эффект; Подходит для детской посуды</t>
+          <t>Для плит, духовок, грилей и мультиварок; Эффективен от жира, нагара и копоти; Эфирные масла: для плит, духовок, грилей и мультиварок</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>1 л</t>
+          <t>500 мл</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
@@ -1740,7 +1744,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>biolut-dish-gel-aloe-sensitive-05l</t>
+          <t>biolut-dish-gel-aloe-sensitive-5l</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1753,14 +1757,10 @@
           <t>Biolut, гель для посуды «Алоэ вера» Sensitive</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Густая формула; Биоразлагаемый состав; Антибактериальный эффект; Подходит для детской посуды</t>
-        </is>
-      </c>
+      <c r="D32" s="3" t="inlineStr"/>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0,5 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
@@ -1780,7 +1780,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>biolut-dish-gel-raspberry-mint-5l</t>
+          <t>biolut-dish-gel-aloe-sensitive-1l</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1790,13 +1790,17 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Biolut, гель для посуды «Малина и мята»</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr"/>
+          <t>Biolut, гель для посуды «Алоэ вера» Sensitive</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Густая формула; Биоразлагаемый состав; Антибактериальный эффект; Подходит для детской посуды</t>
+        </is>
+      </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>1 л</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr"/>
@@ -1816,7 +1820,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>biolut-dish-gel-watermelon-5l</t>
+          <t>biolut-dish-gel-aloe-sensitive-05l</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1826,13 +1830,17 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Biolut, гель для посуды «Сочный арбуз»</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr"/>
+          <t>Biolut, гель для посуды «Алоэ вера» Sensitive</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Густая формула; Биоразлагаемый состав; Антибактериальный эффект; Подходит для детской посуды</t>
+        </is>
+      </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>0,5 л</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
@@ -1852,7 +1860,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>biolut-dish-gel-lemon-5l</t>
+          <t>biolut-dish-gel-raspberry-mint-5l</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1862,7 +1870,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Biolut, гель для посуды «Сочный лимон»</t>
+          <t>Biolut, гель для посуды «Малина и мята»</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr"/>
@@ -1888,7 +1896,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>biolut-dish-gel-lemon-1l</t>
+          <t>biolut-dish-gel-watermelon-5l</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1898,17 +1906,13 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Biolut, гель для посуды «Сочный лимон»</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Густая формула; Биоразлагаемый состав; Подходит для детской посуды</t>
-        </is>
-      </c>
+          <t>Biolut, гель для посуды «Сочный арбуз»</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr"/>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>1 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr"/>
@@ -1928,7 +1932,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>biolut-dish-gel-lemon-05l</t>
+          <t>biolut-dish-gel-lemon-5l</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1941,14 +1945,10 @@
           <t>Biolut, гель для посуды «Сочный лимон»</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Густая формула; Биоразлагаемый состав; Подходит для детской посуды</t>
-        </is>
-      </c>
+      <c r="D37" s="3" t="inlineStr"/>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>0,5 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr"/>
@@ -1968,7 +1968,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>melta-chudo-pasta-1kg</t>
+          <t>biolut-dish-gel-lemon-1l</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1978,17 +1978,17 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Melta Чудо-паста, универсальная чистящая паста, 100+ применений</t>
+          <t>Biolut, гель для посуды «Сочный лимон»</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>100+ применений</t>
+          <t>Густая формула; Биоразлагаемый состав; Подходит для детской посуды</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>1 кг</t>
+          <t>1 л</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr"/>
@@ -2008,7 +2008,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>melta-laundry-gel-color-6l</t>
+          <t>biolut-dish-gel-lemon-05l</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2018,17 +2018,17 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Melta, гель для стирки для цветного, концентрированная формула, 190 стирок</t>
+          <t>Biolut, гель для посуды «Сочный лимон»</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Концентрированная формула; 190 стирок</t>
+          <t>Густая формула; Биоразлагаемый состав; Подходит для детской посуды</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>6 л</t>
+          <t>0,5 л</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr"/>
@@ -2048,7 +2048,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>melta-laundry-gel-color-2l</t>
+          <t>melta-chudo-pasta-1kg</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2058,17 +2058,17 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Melta, гель для стирки для цветного, концентрированная формула, 40 стирок</t>
+          <t>Melta Чудо-паста, универсальная чистящая паста, 100+ применений</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Концентрированная формула; 40 стирок</t>
+          <t>100+ применений</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>2 л</t>
+          <t>1 кг</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr"/>
@@ -2088,7 +2088,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>melta-laundry-gel-universal-6l</t>
+          <t>melta-laundry-gel-color-6l</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Melta, гель для стирки универсальный, концентрированная формула, 190 стирок</t>
+          <t>Melta, гель для стирки для цветного, концентрированная формула, 190 стирок</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -2128,7 +2128,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>melta-laundry-gel-universal-2l</t>
+          <t>melta-laundry-gel-color-2l</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Melta, гель для стирки универсальный, концентрированная формула, 40 стирок</t>
+          <t>Melta, гель для стирки для цветного, концентрированная формула, 40 стирок</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -2168,7 +2168,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>melta-oxygen-1kg</t>
+          <t>melta-laundry-gel-universal-6l</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2178,17 +2178,17 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Melta, пятновыводитель-отбеливатель с активным кислородом «№1 средство для всего», 100+ применений</t>
+          <t>Melta, гель для стирки универсальный, концентрированная формула, 190 стирок</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>100+ применений; №1 средство для всего</t>
+          <t>Концентрированная формула; 190 стирок</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>1 кг</t>
+          <t>6 л</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr"/>
@@ -2208,7 +2208,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>mitti-laundry-gel-universal-6l</t>
+          <t>melta-laundry-gel-universal-2l</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2218,17 +2218,17 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Mitti, гель для стирки универсальный (этикетка PL/RU), 195 стирок</t>
+          <t>Melta, гель для стирки универсальный, концентрированная формула, 40 стирок</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>195 стирок</t>
+          <t>Концентрированная формула; 40 стирок</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>6 л</t>
+          <t>2 л</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr"/>
@@ -2248,7 +2248,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>tirex-granules</t>
+          <t>melta-oxygen-1kg</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2258,11 +2258,19 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Tirex Granules, гранулы от засоров</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="4" t="inlineStr"/>
+          <t>Melta, пятновыводитель-отбеливатель с активным кислородом «№1 средство для всего», 100+ применений</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>100+ применений; №1 средство для всего</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>1 кг</t>
+        </is>
+      </c>
       <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="inlineStr"/>
       <c r="H45" s="4" t="inlineStr"/>
@@ -2280,27 +2288,27 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>melta-pets-paw-nose-wax-120ml</t>
+          <t>mitti-laundry-gel-universal-6l</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Для животных</t>
+          <t>Бытовая химия</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Melta for pets, воск для лап и носа «Защита и регенерация», с витамином E</t>
+          <t>Mitti, гель для стирки универсальный (этикетка PL/RU), 195 стирок</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>С витамином E</t>
+          <t>195 стирок</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>120 мл</t>
+          <t>6 л</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr"/>
@@ -2320,24 +2328,20 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>melta-pets-paw-foam</t>
+          <t>tirex-granules</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Для животных</t>
+          <t>Бытовая химия</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Melta for pets, пенка для лапок D-пантенол + хлоргексидин, не требует смывания</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Не требует смывания</t>
-        </is>
-      </c>
+          <t>Tirex Granules, гранулы от засоров</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr"/>
       <c r="E47" s="4" t="inlineStr"/>
       <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="inlineStr"/>
@@ -2356,7 +2360,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>melta-pets-paw-foam-brush</t>
+          <t>melta-pets-paw-nose-wax-120ml</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -2366,15 +2370,19 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Melta for pets, пенка для лапок с массажной щёткой, D-пантенол + хлоргексидин, не требует смывания</t>
+          <t>Melta for pets, воск для лап и носа «Защита и регенерация», с витамином E</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Не требует смывания</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr"/>
+          <t>С витамином E</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>120 мл</t>
+        </is>
+      </c>
       <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="inlineStr"/>
       <c r="H48" s="4" t="inlineStr"/>
@@ -2392,7 +2400,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>melta-pets-shampoo-dogs-cats-fleas</t>
+          <t>melta-pets-paw-foam</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -2402,19 +2410,15 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Melta for pets, шампунь для собак и кошек от блох и клещей</t>
+          <t>Melta for pets, пенка для лапок D-пантенол + хлоргексидин, не требует смывания</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Для собак и кошек; От блох и клещей</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>500 мл</t>
-        </is>
-      </c>
+          <t>Не требует смывания</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr"/>
       <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="inlineStr"/>
       <c r="H49" s="4" t="inlineStr"/>
@@ -2432,7 +2436,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>melta-pets-shampoo-dogs-fleas</t>
+          <t>melta-pets-paw-foam-brush</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -2442,19 +2446,15 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Melta for pets, шампунь для собак от блох и клещей</t>
+          <t>Melta for pets, пенка для лапок с массажной щёткой, D-пантенол + хлоргексидин, не требует смывания</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>От блох и клещей</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>500 мл</t>
-        </is>
-      </c>
+          <t>Не требует смывания</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr"/>
       <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="inlineStr"/>
       <c r="H50" s="4" t="inlineStr"/>
@@ -2472,7 +2472,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>melta-pets-shampoo-dogs</t>
+          <t>melta-pets-shampoo-dogs-cats-fleas</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -2482,10 +2482,14 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Melta for pets, шампунь для собак с Д-пантенолом</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr"/>
+          <t>Melta for pets, шампунь для собак и кошек от блох и клещей</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Для собак и кошек; От блох и клещей</t>
+        </is>
+      </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
           <t>500 мл</t>
@@ -2508,27 +2512,27 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>biolut-liquid-soap-aloe-5l</t>
+          <t>melta-pets-shampoo-dogs-fleas</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Мыло</t>
+          <t>Для животных</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Biolut Antibacterial, жидкое мыло Aloe Vera</t>
+          <t>Melta for pets, шампунь для собак от блох и клещей</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Деликатное очищение; 100% смывается с кожи; Эффективная защита от бактерий</t>
+          <t>От блох и клещей</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>500 мл</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr"/>
@@ -2548,27 +2552,23 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>biolut-liquid-soap-aloe-05l</t>
+          <t>melta-pets-shampoo-dogs</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Мыло</t>
+          <t>Для животных</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Biolut Antibacterial, жидкое мыло Aloe Vera</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Деликатное очищение; 100% смывается с кожи; Эффективная защита от бактерий</t>
-        </is>
-      </c>
+          <t>Melta for pets, шампунь для собак с Д-пантенолом</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr"/>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>0,5 л</t>
+          <t>500 мл</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr"/>
